--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488177_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488177_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.6274</v>
+        <v>5.4726</v>
       </c>
       <c r="E2" t="n">
-        <v>3.1523</v>
+        <v>3.7514</v>
       </c>
       <c r="F2" t="n">
-        <v>1.475</v>
+        <v>1.7213</v>
       </c>
       <c r="G2" t="n">
         <v>2.8622</v>
@@ -610,13 +610,13 @@
         <v>3.7057</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.0147</v>
+        <v>-0.1694</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8667</v>
+        <v>-0.2676</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.148</v>
+        <v>0.0982</v>
       </c>
       <c r="V2" t="n">
         <v>0.0005</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.5952</v>
+        <v>4.6964</v>
       </c>
       <c r="E3" t="n">
-        <v>1.6339</v>
+        <v>2.1782</v>
       </c>
       <c r="F3" t="n">
-        <v>2.9614</v>
+        <v>2.5182</v>
       </c>
       <c r="G3" t="n">
         <v>2.0076</v>
@@ -688,13 +688,13 @@
         <v>3.3352</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1124</v>
+        <v>0.2136</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5931</v>
+        <v>-0.0488</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7056</v>
+        <v>0.2624</v>
       </c>
       <c r="V3" t="n">
         <v>0.2518</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.692</v>
+        <v>2.1569</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.2917</v>
+        <v>-0.4328</v>
       </c>
       <c r="F4" t="n">
-        <v>2.9836</v>
+        <v>2.5897</v>
       </c>
       <c r="G4" t="n">
         <v>1.1024</v>
@@ -766,13 +766,13 @@
         <v>2.7793</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5792</v>
+        <v>0.0441</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2897</v>
+        <v>-0.4309</v>
       </c>
       <c r="U4" t="n">
-        <v>0.869</v>
+        <v>0.475</v>
       </c>
       <c r="V4" t="n">
         <v>1.1956</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. IDRIS IGENE</t>
+          <t>A. RODRIGUEZ LEIRO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6894</v>
+        <v>0.8027</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.8933</v>
+        <v>0.0504</v>
       </c>
       <c r="F5" t="n">
-        <v>2.5827</v>
+        <v>0.7523</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.4969</v>
+        <v>-0.4604</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.795</v>
+        <v>-0.5635</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2981</v>
+        <v>0.1031</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.8417</v>
+        <v>0.9258</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.2717</v>
+        <v>0.8844</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.5699</v>
+        <v>0.0415</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.6552</v>
+        <v>-1.3863</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.5233</v>
+        <v>-1.4478</v>
       </c>
       <c r="O5" t="n">
-        <v>0.868</v>
+        <v>0.0616</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.4823</v>
+        <v>1.6676</v>
       </c>
       <c r="Q5" t="n">
-        <v>-4.6322</v>
+        <v>-1.1117</v>
       </c>
       <c r="R5" t="n">
-        <v>3.1499</v>
+        <v>2.7793</v>
       </c>
       <c r="S5" t="n">
-        <v>2.4097</v>
+        <v>-0.0274</v>
       </c>
       <c r="T5" t="n">
-        <v>2.3217</v>
+        <v>0.2363</v>
       </c>
       <c r="U5" t="n">
-        <v>0.08799999999999999</v>
+        <v>-0.2636</v>
       </c>
       <c r="V5" t="n">
-        <v>1.2589</v>
+        <v>-0.3771</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.3771</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. OSÉS BERNALDÉZ</t>
+          <t>P. OSES BERNALDEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6441</v>
+        <v>0.7043</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6441</v>
+        <v>-1.0526</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1.7569</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6441</v>
+        <v>-0.4581</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6441</v>
+        <v>0.3528</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>-0.8110000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6441</v>
+        <v>0.6293</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6441</v>
+        <v>1.2406</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>-1.0874</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-0.8878</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>-0.1996</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.1117</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.0382</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>3.1499</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>0.4284</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>0.3563</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>0.0721</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.3777</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.3777</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. RODRÍGUEZ LEIRO</t>
+          <t>P. OSÉS BERNALDÉZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,31 +955,31 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6221</v>
+        <v>0.6441</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6221</v>
+        <v>0.6441</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6221</v>
+        <v>0.6441</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>0.6441</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6221</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6221</v>
+        <v>0.6441</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>0.6441</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6221</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ LEIRO</t>
+          <t>A. RODRÍGUEZ LEIRO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5018</v>
+        <v>0.6221</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0043</v>
+        <v>0.6221</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5061</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.4604</v>
+        <v>0.6221</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5635</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1031</v>
+        <v>0.6221</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9258</v>
+        <v>0.6221</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8844</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0415</v>
+        <v>0.6221</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.3863</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.4478</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0616</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.6676</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1117</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.7793</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3283</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1816</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5099</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.3771</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.3771</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. OSES BERNALDEZ</t>
+          <t>J. PAREDES BERMEJO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1851</v>
+        <v>-0.2078</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.6949</v>
+        <v>0.1072</v>
       </c>
       <c r="F9" t="n">
-        <v>1.88</v>
+        <v>-0.315</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4581</v>
+        <v>-0.8965</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3528</v>
+        <v>-0.5693</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.8110000000000001</v>
+        <v>-0.3272</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6293</v>
+        <v>0.1302</v>
       </c>
       <c r="K9" t="n">
-        <v>1.2406</v>
+        <v>0.1503</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6114000000000001</v>
+        <v>-0.0201</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.0874</v>
+        <v>-1.0267</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8878</v>
+        <v>-0.7196</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1996</v>
+        <v>-0.3071</v>
       </c>
       <c r="P9" t="n">
         <v>1.1117</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.0382</v>
+        <v>-0.1853</v>
       </c>
       <c r="R9" t="n">
-        <v>3.1499</v>
+        <v>1.297</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.09080000000000001</v>
+        <v>-0.0454</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.286</v>
+        <v>0.1623</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1952</v>
+        <v>-0.2077</v>
       </c>
       <c r="V9" t="n">
         <v>-0.3777</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. PAREDES BERMEJO</t>
+          <t>R. ALOGO EVUNA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5268</v>
+        <v>-1.004</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0887</v>
+        <v>-1.0196</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4381</v>
+        <v>0.0156</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.8965</v>
+        <v>-0.8453000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5693</v>
+        <v>-0.1219</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3272</v>
+        <v>-0.7235</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1302</v>
+        <v>-0.3726</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1503</v>
+        <v>0.8501</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.0201</v>
+        <v>-1.2228</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.0267</v>
+        <v>-0.4727</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7196</v>
+        <v>-0.972</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3071</v>
+        <v>0.4993</v>
       </c>
       <c r="P10" t="n">
-        <v>1.1117</v>
+        <v>1.6676</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.1853</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.297</v>
+        <v>1.6676</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3644</v>
+        <v>-0.5674</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0336</v>
+        <v>-0.6469</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3308</v>
+        <v>0.0796</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.3777</v>
+        <v>-1.2589</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.3777</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R. ALOGO EVUNA</t>
+          <t>S. IDRIS IGENE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.3536</v>
+        <v>-1.0864</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.1722</v>
+        <v>-3.6445</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1814</v>
+        <v>2.558</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.8453000000000001</v>
+        <v>-1.4969</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1219</v>
+        <v>-1.795</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7235</v>
+        <v>0.2981</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.3726</v>
+        <v>-0.8417</v>
       </c>
       <c r="K11" t="n">
-        <v>0.8501</v>
+        <v>-0.2717</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.2228</v>
+        <v>-0.5699</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.4727</v>
+        <v>-0.6552</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.972</v>
+        <v>-1.5233</v>
       </c>
       <c r="O11" t="n">
-        <v>0.4993</v>
+        <v>0.868</v>
       </c>
       <c r="P11" t="n">
-        <v>1.6676</v>
+        <v>-1.4823</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-4.6322</v>
       </c>
       <c r="R11" t="n">
-        <v>1.6676</v>
+        <v>3.1499</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.917</v>
+        <v>0.6339</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7996</v>
+        <v>0.5705</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1174</v>
+        <v>0.0634</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.2589</v>
+        <v>1.2589</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2589</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.208</v>
+        <v>-1.7851</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.5256</v>
+        <v>-2.2751</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3176</v>
+        <v>0.49</v>
       </c>
       <c r="G12" t="n">
         <v>-1.3247</v>
@@ -1390,13 +1390,13 @@
         <v>1.297</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6598000000000001</v>
+        <v>-0.2369</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4924</v>
+        <v>-0.2419</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1674</v>
+        <v>0.005</v>
       </c>
       <c r="V12" t="n">
         <v>1.2589</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>10.4687</v>
+        <v>11.0158</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.6183</v>
+        <v>-1.0712</v>
       </c>
       <c r="F13" t="n">
-        <v>12.0869</v>
+        <v>12.087</v>
       </c>
       <c r="G13" t="n">
         <v>1.7565</v>
@@ -1441,7 +1441,7 @@
         <v>-0.1149000000000002</v>
       </c>
       <c r="J13" t="n">
-        <v>9.324699999999998</v>
+        <v>9.3247</v>
       </c>
       <c r="K13" t="n">
         <v>12.244</v>
@@ -1468,13 +1468,13 @@
         <v>23.1609</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2736999999999999</v>
+        <v>0.2735</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8577999999999999</v>
+        <v>-0.3107000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5843</v>
+        <v>0.5844</v>
       </c>
       <c r="V13" t="n">
         <v>1.5743</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. LARA CALDERA</t>
+          <t>J. LOPEZ YUSTE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.968</v>
+        <v>1.6038</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.4378</v>
+        <v>0.6724</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4058</v>
+        <v>0.9313</v>
       </c>
       <c r="G14" t="n">
-        <v>1.0357</v>
+        <v>-0.7354000000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.1747</v>
+        <v>-0.0562</v>
       </c>
       <c r="I14" t="n">
-        <v>1.2105</v>
+        <v>-0.6791</v>
       </c>
       <c r="J14" t="n">
-        <v>2.9935</v>
+        <v>0.7466</v>
       </c>
       <c r="K14" t="n">
-        <v>2.2364</v>
+        <v>2.0096</v>
       </c>
       <c r="L14" t="n">
-        <v>0.7572</v>
+        <v>-1.263</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.9578</v>
+        <v>-1.4819</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.4111</v>
+        <v>-2.0658</v>
       </c>
       <c r="O14" t="n">
-        <v>0.4533</v>
+        <v>0.5839</v>
       </c>
       <c r="P14" t="n">
-        <v>-3.5205</v>
+        <v>2.9646</v>
       </c>
       <c r="Q14" t="n">
-        <v>-6.485</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>2.9646</v>
       </c>
       <c r="S14" t="n">
-        <v>0.62</v>
+        <v>0.319</v>
       </c>
       <c r="T14" t="n">
-        <v>0.536</v>
+        <v>-0.3886</v>
       </c>
       <c r="U14" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.7075</v>
       </c>
       <c r="V14" t="n">
-        <v>2.8327</v>
+        <v>-0.9444</v>
       </c>
       <c r="W14" t="n">
-        <v>2.5177</v>
+        <v>0.3144</v>
       </c>
       <c r="X14" t="n">
-        <v>0.315</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. LÓPEZ YUSTE</t>
+          <t>L. DALLACOSTA ORTIZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6221</v>
+        <v>0.9476</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6221</v>
+        <v>0.8411999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>0.1063</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6221</v>
+        <v>0.8504</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>-0.3046</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6221</v>
+        <v>1.155</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6221</v>
+        <v>1.8137</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1.1809</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6221</v>
+        <v>0.6327</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>-0.9633</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>-1.4855</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>0.5223</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>0.3706</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.297</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>0.041</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>-0.046</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>L. DALLACOSTA ORTIZ</t>
+          <t>D. LARA CALDERA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3686</v>
+        <v>0.7229</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4495</v>
+        <v>-1.0254</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0809</v>
+        <v>1.7483</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8504</v>
+        <v>1.0357</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.3046</v>
+        <v>-0.1747</v>
       </c>
       <c r="I16" t="n">
-        <v>1.155</v>
+        <v>1.2105</v>
       </c>
       <c r="J16" t="n">
-        <v>1.8137</v>
+        <v>2.9935</v>
       </c>
       <c r="K16" t="n">
-        <v>1.1809</v>
+        <v>2.2364</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6327</v>
+        <v>0.7572</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.9633</v>
+        <v>-1.9578</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.4855</v>
+        <v>-2.4111</v>
       </c>
       <c r="O16" t="n">
-        <v>0.5223</v>
+        <v>0.4533</v>
       </c>
       <c r="P16" t="n">
-        <v>0.3706</v>
+        <v>-3.5205</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9264</v>
+        <v>-6.485</v>
       </c>
       <c r="R16" t="n">
-        <v>1.297</v>
+        <v>2.9646</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.538</v>
+        <v>0.3749</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4377</v>
+        <v>-0.0516</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1002</v>
+        <v>0.4265</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.3144</v>
+        <v>2.8327</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.5177</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.3144</v>
+        <v>0.315</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. LOPEZ YUSTE</t>
+          <t>J. LÓPEZ YUSTE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3559</v>
+        <v>0.6221</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3069</v>
+        <v>0.6221</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6627</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.7354000000000001</v>
+        <v>0.6221</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0562</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.6791</v>
+        <v>0.6221</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7466</v>
+        <v>0.6221</v>
       </c>
       <c r="K17" t="n">
-        <v>2.0096</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.263</v>
+        <v>0.6221</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.4819</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.0658</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5839</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.9646</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.9646</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9288999999999999</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.3679</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4389</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.9444</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2589</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. CABALLERO CARPIO</t>
+          <t>F. GONZALEZ ROSCO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3145</v>
+        <v>0.1584</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6411</v>
+        <v>-0.9282</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3266</v>
+        <v>1.0867</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.5401</v>
+        <v>0.349</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.2559</v>
+        <v>0.372</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2841</v>
+        <v>-0.023</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0429</v>
+        <v>0.0644</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0429</v>
+        <v>0.0644</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.583</v>
+        <v>0.2846</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2989</v>
+        <v>0.3076</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2841</v>
+        <v>-0.023</v>
       </c>
       <c r="P18" t="n">
-        <v>0.3706</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R18" t="n">
-        <v>0.3706</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S18" t="n">
-        <v>0.484</v>
+        <v>0.18</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5981</v>
+        <v>-0.06619999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1142</v>
+        <v>0.2462</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>F. GONZALEZ ROSCO</t>
+          <t>S. CABALLERO CARPIO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0872</v>
+        <v>-0.0526</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.0262</v>
+        <v>0.2494</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9389</v>
+        <v>-0.302</v>
       </c>
       <c r="G19" t="n">
-        <v>0.349</v>
+        <v>-0.5401</v>
       </c>
       <c r="H19" t="n">
-        <v>0.372</v>
+        <v>-0.2559</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.023</v>
+        <v>-0.2841</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0644</v>
+        <v>0.0429</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0644</v>
+        <v>0.0429</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2846</v>
+        <v>-0.583</v>
       </c>
       <c r="N19" t="n">
-        <v>0.3076</v>
+        <v>-0.2989</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.023</v>
+        <v>-0.2841</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.3706</v>
+        <v>0.3706</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.3706</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.06569999999999999</v>
+        <v>0.1169</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1641</v>
+        <v>0.2064</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0985</v>
+        <v>-0.0895</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G. MAIGA</t>
+          <t>L. LOPEZ CALZADA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.1672</v>
+        <v>-0.7806999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.2306</v>
+        <v>-0.5632</v>
       </c>
       <c r="F20" t="n">
-        <v>1.0634</v>
+        <v>-0.2175</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.3644</v>
+        <v>-0.2918</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.326</v>
+        <v>0.9355</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9616</v>
+        <v>-1.2273</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7203000000000001</v>
+        <v>0.9611</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.0262</v>
+        <v>2.7953</v>
       </c>
       <c r="L20" t="n">
-        <v>0.7465000000000001</v>
+        <v>-1.8342</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.0847</v>
+        <v>-1.253</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.2998</v>
+        <v>-1.8598</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2152</v>
+        <v>0.6069</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.594</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-4.6322</v>
+        <v>-1.8529</v>
       </c>
       <c r="R20" t="n">
-        <v>2.0382</v>
+        <v>1.8529</v>
       </c>
       <c r="S20" t="n">
-        <v>1.7912</v>
+        <v>0.1411</v>
       </c>
       <c r="T20" t="n">
-        <v>1.6813</v>
+        <v>-0.3003</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1099</v>
+        <v>0.4414</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.63</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.6289</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>L. LOPEZ CALZADA</t>
+          <t>G. MAIGA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.2056</v>
+        <v>-2.1224</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.759</v>
+        <v>-3.5036</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.4466</v>
+        <v>1.3812</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.2918</v>
+        <v>-0.3644</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9355</v>
+        <v>-1.326</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.2273</v>
+        <v>0.9616</v>
       </c>
       <c r="J21" t="n">
-        <v>0.9611</v>
+        <v>0.7203000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>2.7953</v>
+        <v>-0.0262</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.8342</v>
+        <v>0.7465000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.253</v>
+        <v>-1.0847</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.8598</v>
+        <v>-1.2998</v>
       </c>
       <c r="O21" t="n">
-        <v>0.6069</v>
+        <v>0.2152</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>-2.594</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.8529</v>
+        <v>-4.6322</v>
       </c>
       <c r="R21" t="n">
-        <v>1.8529</v>
+        <v>2.0382</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2838</v>
+        <v>0.836</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4961</v>
+        <v>0.4082</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2124</v>
+        <v>0.4278</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.63</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.6289</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2589</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.3984</v>
+        <v>-3.2266</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.564</v>
+        <v>-2.4661</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.8345</v>
+        <v>-0.7606000000000001</v>
       </c>
       <c r="G22" t="n">
         <v>-0.8371</v>
@@ -2170,13 +2170,13 @@
         <v>0.7411</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1908</v>
+        <v>-0.019</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1641</v>
+        <v>-0.06619999999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0266</v>
+        <v>0.0473</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2589</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.2393</v>
+        <v>-6.3826</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.4753</v>
+        <v>-5.9856</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.764</v>
+        <v>-0.3969</v>
       </c>
       <c r="G23" t="n">
         <v>-1.8449</v>
@@ -2248,13 +2248,13 @@
         <v>2.9646</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6146</v>
+        <v>0.2422</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7697000000000001</v>
+        <v>-0.2801</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1552</v>
+        <v>0.5223</v>
       </c>
       <c r="V23" t="n">
         <v>-1.2594</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-10.4686</v>
+        <v>-8.5101</v>
       </c>
       <c r="E24" t="n">
-        <v>-12.0871</v>
+        <v>-12.087</v>
       </c>
       <c r="F24" t="n">
-        <v>1.6182</v>
+        <v>3.576799999999999</v>
       </c>
       <c r="G24" t="n">
         <v>-1.7565</v>
@@ -2326,13 +2326,13 @@
         <v>15.7495</v>
       </c>
       <c r="S24" t="n">
-        <v>0.2734000000000002</v>
+        <v>2.2321</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5841999999999999</v>
+        <v>-0.5844</v>
       </c>
       <c r="U24" t="n">
-        <v>0.8579000000000001</v>
+        <v>2.8165</v>
       </c>
       <c r="V24" t="n">
         <v>-1.5744</v>
